--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -2682,10 +2682,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119520924</v>
+        <v>119520926</v>
       </c>
       <c r="B20" t="n">
-        <v>90846</v>
+        <v>96862</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2694,25 +2694,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586172</v>
+        <v>586260</v>
       </c>
       <c r="R20" t="n">
-        <v>6617796</v>
+        <v>6617641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2768,11 +2768,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2793,10 +2788,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119520926</v>
+        <v>119520924</v>
       </c>
       <c r="B21" t="n">
-        <v>96862</v>
+        <v>90846</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2805,25 +2800,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2833,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586260</v>
+        <v>586172</v>
       </c>
       <c r="R21" t="n">
-        <v>6617641</v>
+        <v>6617796</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2879,6 +2874,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119520940</v>
+        <v>119520947</v>
       </c>
       <c r="B22" t="n">
-        <v>90954</v>
+        <v>84434</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2915,32 +2915,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6040186</v>
+        <v>241</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gransotdyna</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hemfallet ost, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586307</v>
+        <v>586205</v>
       </c>
       <c r="R22" t="n">
-        <v>6617819</v>
+        <v>6618085</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2981,7 +2983,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3009,10 +3010,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119520947</v>
+        <v>119520940</v>
       </c>
       <c r="B23" t="n">
-        <v>84434</v>
+        <v>90954</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3025,34 +3026,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>241</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Gransotdyna</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hemfallet ost, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586205</v>
+        <v>586307</v>
       </c>
       <c r="R23" t="n">
-        <v>6618085</v>
+        <v>6617819</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3093,6 +3092,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119520947</v>
+        <v>119520940</v>
       </c>
       <c r="B22" t="n">
-        <v>84434</v>
+        <v>90954</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2915,34 +2915,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>241</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Gransotdyna</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hemfallet ost, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586205</v>
+        <v>586307</v>
       </c>
       <c r="R22" t="n">
-        <v>6618085</v>
+        <v>6617819</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2983,6 +2981,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3010,10 +3009,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119520940</v>
+        <v>119520947</v>
       </c>
       <c r="B23" t="n">
-        <v>90954</v>
+        <v>84434</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3026,32 +3025,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>241</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gransotdyna</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hemfallet ost, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586307</v>
+        <v>586205</v>
       </c>
       <c r="R23" t="n">
-        <v>6617819</v>
+        <v>6618085</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3092,7 +3093,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119520887</v>
+        <v>119520936</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586302</v>
+        <v>586297</v>
       </c>
       <c r="R3" t="n">
-        <v>6617824</v>
+        <v>6617629</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,7 +899,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -921,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119520911</v>
+        <v>119520958</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>100171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,25 +933,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586243</v>
+        <v>586121</v>
       </c>
       <c r="R4" t="n">
-        <v>6617585</v>
+        <v>6617737</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,11 +1007,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1032,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119520910</v>
+        <v>119520952</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>91182</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,25 +1039,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586131</v>
+        <v>586285</v>
       </c>
       <c r="R5" t="n">
-        <v>6617749</v>
+        <v>6617973</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119520936</v>
+        <v>119520904</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,25 +1150,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586297</v>
+        <v>586216</v>
       </c>
       <c r="R6" t="n">
-        <v>6617629</v>
+        <v>6618082</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1227,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1254,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119520901</v>
+        <v>119520924</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,21 +1265,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586252</v>
+        <v>586172</v>
       </c>
       <c r="R7" t="n">
-        <v>6618078</v>
+        <v>6617796</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119520900</v>
+        <v>119520941</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>90954</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,34 +1376,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemfallet ost, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586320</v>
+        <v>586301</v>
       </c>
       <c r="R8" t="n">
-        <v>6617975</v>
+        <v>6617822</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,6 +1442,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1476,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119520904</v>
+        <v>119520940</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>90954</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,34 +1486,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hemfallet ost, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586216</v>
+        <v>586307</v>
       </c>
       <c r="R9" t="n">
-        <v>6618082</v>
+        <v>6617819</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,6 +1552,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1587,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119520898</v>
+        <v>119520921</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>94431</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,25 +1592,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1627,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586282</v>
+        <v>586238</v>
       </c>
       <c r="R10" t="n">
-        <v>6617889</v>
+        <v>6617657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,11 +1666,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1698,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119520945</v>
+        <v>119520887</v>
       </c>
       <c r="B11" t="n">
-        <v>90966</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,25 +1698,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5420</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586251</v>
+        <v>586302</v>
       </c>
       <c r="R11" t="n">
-        <v>6618064</v>
+        <v>6617824</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,6 +1772,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1804,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119520935</v>
+        <v>119520949</v>
       </c>
       <c r="B12" t="n">
-        <v>96865</v>
+        <v>5169</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221946</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586287</v>
+        <v>586210</v>
       </c>
       <c r="R12" t="n">
-        <v>6617697</v>
+        <v>6617608</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119520914</v>
+        <v>119520937</v>
       </c>
       <c r="B13" t="n">
-        <v>94414</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,25 +1915,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2668</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1950,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586225</v>
+        <v>586316</v>
       </c>
       <c r="R13" t="n">
-        <v>6617957</v>
+        <v>6617624</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,7 +1992,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>sten</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2132,7 +2125,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119520884</v>
+        <v>119520891</v>
       </c>
       <c r="B15" t="n">
         <v>90562</v>
@@ -2172,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586282</v>
+        <v>586172</v>
       </c>
       <c r="R15" t="n">
-        <v>6617692</v>
+        <v>6617792</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119520950</v>
+        <v>119520899</v>
       </c>
       <c r="B16" t="n">
-        <v>91182</v>
+        <v>90562</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2248,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2276,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586301</v>
+        <v>586273</v>
       </c>
       <c r="R16" t="n">
-        <v>6617823</v>
+        <v>6617963</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,10 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119520895</v>
+        <v>119520950</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
+        <v>91182</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,25 +2359,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2394,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586158</v>
+        <v>586301</v>
       </c>
       <c r="R17" t="n">
-        <v>6617877</v>
+        <v>6617823</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,7 +2458,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119520908</v>
+        <v>119520897</v>
       </c>
       <c r="B18" t="n">
         <v>90562</v>
@@ -2505,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586108</v>
+        <v>586273</v>
       </c>
       <c r="R18" t="n">
-        <v>6617800</v>
+        <v>6617904</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119520949</v>
+        <v>119520884</v>
       </c>
       <c r="B19" t="n">
-        <v>5169</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2588,25 +2581,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2616,10 +2609,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586210</v>
+        <v>586282</v>
       </c>
       <c r="R19" t="n">
-        <v>6617608</v>
+        <v>6617692</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2662,6 +2655,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2682,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119520926</v>
+        <v>119520898</v>
       </c>
       <c r="B20" t="n">
-        <v>96862</v>
+        <v>90562</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2694,25 +2692,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2722,10 +2720,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586260</v>
+        <v>586282</v>
       </c>
       <c r="R20" t="n">
-        <v>6617641</v>
+        <v>6617889</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2768,6 +2766,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2788,10 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119520924</v>
+        <v>119520917</v>
       </c>
       <c r="B21" t="n">
-        <v>90846</v>
+        <v>94431</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2800,25 +2803,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>2818</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2828,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586172</v>
+        <v>586270</v>
       </c>
       <c r="R21" t="n">
-        <v>6617796</v>
+        <v>6617962</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2874,11 +2877,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2899,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119520940</v>
+        <v>119520883</v>
       </c>
       <c r="B22" t="n">
-        <v>90954</v>
+        <v>90905</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2911,36 +2909,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6040186</v>
+        <v>2062</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hemfallet ost, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586307</v>
+        <v>586204</v>
       </c>
       <c r="R22" t="n">
-        <v>6617819</v>
+        <v>6618090</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2981,13 +2981,12 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>ullticka</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3009,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119520947</v>
+        <v>119520926</v>
       </c>
       <c r="B23" t="n">
-        <v>84434</v>
+        <v>96862</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3021,25 +3020,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>241</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3049,10 +3048,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586205</v>
+        <v>586260</v>
       </c>
       <c r="R23" t="n">
-        <v>6618085</v>
+        <v>6617641</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3095,11 +3094,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3120,7 +3114,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119520913</v>
+        <v>119520885</v>
       </c>
       <c r="B24" t="n">
         <v>90562</v>
@@ -3160,10 +3154,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586263</v>
+        <v>586294</v>
       </c>
       <c r="R24" t="n">
-        <v>6617656</v>
+        <v>6617710</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,10 +3225,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119520952</v>
+        <v>119520913</v>
       </c>
       <c r="B25" t="n">
-        <v>91182</v>
+        <v>90562</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3243,25 +3237,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3271,10 +3265,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586285</v>
+        <v>586263</v>
       </c>
       <c r="R25" t="n">
-        <v>6617973</v>
+        <v>6617656</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3342,10 +3336,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119520882</v>
+        <v>119520886</v>
       </c>
       <c r="B26" t="n">
-        <v>90905</v>
+        <v>90562</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3354,25 +3348,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3382,10 +3376,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586339</v>
+        <v>586344</v>
       </c>
       <c r="R26" t="n">
-        <v>6617744</v>
+        <v>6617753</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3431,7 +3425,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>ullticka</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3453,10 +3447,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119520946</v>
+        <v>119520911</v>
       </c>
       <c r="B27" t="n">
-        <v>84434</v>
+        <v>90562</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3469,21 +3463,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>241</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3493,10 +3487,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586183</v>
+        <v>586243</v>
       </c>
       <c r="R27" t="n">
-        <v>6617797</v>
+        <v>6617585</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3564,10 +3558,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119520922</v>
+        <v>119520893</v>
       </c>
       <c r="B28" t="n">
-        <v>91005</v>
+        <v>90562</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3576,25 +3570,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3604,10 +3598,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586289</v>
+        <v>586119</v>
       </c>
       <c r="R28" t="n">
-        <v>6617808</v>
+        <v>6617842</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,10 +3669,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119520903</v>
+        <v>119520922</v>
       </c>
       <c r="B29" t="n">
-        <v>90562</v>
+        <v>91005</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3687,25 +3681,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3715,10 +3709,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586218</v>
+        <v>586289</v>
       </c>
       <c r="R29" t="n">
-        <v>6618100</v>
+        <v>6617808</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3786,7 +3780,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119520892</v>
+        <v>119520901</v>
       </c>
       <c r="B30" t="n">
         <v>90562</v>
@@ -3826,10 +3820,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>586144</v>
+        <v>586252</v>
       </c>
       <c r="R30" t="n">
-        <v>6617819</v>
+        <v>6618078</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,10 +3891,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119520894</v>
+        <v>119520945</v>
       </c>
       <c r="B31" t="n">
-        <v>90562</v>
+        <v>90966</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3909,25 +3903,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>5420</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3937,10 +3931,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>586124</v>
+        <v>586251</v>
       </c>
       <c r="R31" t="n">
-        <v>6617862</v>
+        <v>6618064</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3983,11 +3977,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4008,10 +3997,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119520951</v>
+        <v>119520946</v>
       </c>
       <c r="B32" t="n">
-        <v>91182</v>
+        <v>84434</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4020,25 +4009,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1339</v>
+        <v>241</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4048,10 +4037,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>586314</v>
+        <v>586183</v>
       </c>
       <c r="R32" t="n">
-        <v>6617892</v>
+        <v>6617797</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4119,7 +4108,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119520909</v>
+        <v>119520888</v>
       </c>
       <c r="B33" t="n">
         <v>90562</v>
@@ -4159,10 +4148,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586104</v>
+        <v>586284</v>
       </c>
       <c r="R33" t="n">
-        <v>6617783</v>
+        <v>6617814</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4230,7 +4219,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119520902</v>
+        <v>119520903</v>
       </c>
       <c r="B34" t="n">
         <v>90562</v>
@@ -4270,10 +4259,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>586240</v>
+        <v>586218</v>
       </c>
       <c r="R34" t="n">
-        <v>6618091</v>
+        <v>6618100</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4341,10 +4330,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119520921</v>
+        <v>119520948</v>
       </c>
       <c r="B35" t="n">
-        <v>94431</v>
+        <v>105009</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4357,21 +4346,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2818</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4381,10 +4370,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>586238</v>
+        <v>586283</v>
       </c>
       <c r="R35" t="n">
-        <v>6617657</v>
+        <v>6617615</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4447,10 +4436,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119520944</v>
+        <v>119520902</v>
       </c>
       <c r="B36" t="n">
-        <v>74622</v>
+        <v>90562</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4459,25 +4448,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4487,10 +4476,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>586246</v>
+        <v>586240</v>
       </c>
       <c r="R36" t="n">
-        <v>6617940</v>
+        <v>6618091</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4533,6 +4522,11 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4553,10 +4547,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119520937</v>
+        <v>119520951</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>91182</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4565,25 +4559,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4593,10 +4587,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>586316</v>
+        <v>586314</v>
       </c>
       <c r="R37" t="n">
-        <v>6617624</v>
+        <v>6617892</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4642,7 +4636,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4664,10 +4658,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119520941</v>
+        <v>119520894</v>
       </c>
       <c r="B38" t="n">
-        <v>90954</v>
+        <v>90562</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4680,32 +4674,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hemfallet ost, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>586301</v>
+        <v>586124</v>
       </c>
       <c r="R38" t="n">
-        <v>6617822</v>
+        <v>6617862</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4746,7 +4742,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4774,10 +4769,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119520899</v>
+        <v>119520938</v>
       </c>
       <c r="B39" t="n">
-        <v>90562</v>
+        <v>90913</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4790,21 +4785,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>2064</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4814,10 +4809,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>586273</v>
+        <v>586205</v>
       </c>
       <c r="R39" t="n">
-        <v>6617963</v>
+        <v>6618101</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4885,10 +4880,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119520888</v>
+        <v>119520935</v>
       </c>
       <c r="B40" t="n">
-        <v>90562</v>
+        <v>96865</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4897,25 +4892,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>221946</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4925,10 +4920,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>586284</v>
+        <v>586287</v>
       </c>
       <c r="R40" t="n">
-        <v>6617814</v>
+        <v>6617697</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4971,11 +4966,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4996,10 +4986,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119520917</v>
+        <v>119520910</v>
       </c>
       <c r="B41" t="n">
-        <v>94431</v>
+        <v>90562</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5008,25 +4998,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5036,10 +5026,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>586270</v>
+        <v>586131</v>
       </c>
       <c r="R41" t="n">
-        <v>6617962</v>
+        <v>6617749</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5082,6 +5072,11 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5102,10 +5097,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119520938</v>
+        <v>119520944</v>
       </c>
       <c r="B42" t="n">
-        <v>90913</v>
+        <v>74622</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5114,25 +5109,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2064</v>
+        <v>6439</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5142,10 +5137,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>586205</v>
+        <v>586246</v>
       </c>
       <c r="R42" t="n">
-        <v>6618101</v>
+        <v>6617940</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5188,11 +5183,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5213,7 +5203,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119520883</v>
+        <v>119520882</v>
       </c>
       <c r="B43" t="n">
         <v>90905</v>
@@ -5253,10 +5243,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>586204</v>
+        <v>586339</v>
       </c>
       <c r="R43" t="n">
-        <v>6618090</v>
+        <v>6617744</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5324,7 +5314,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119520885</v>
+        <v>119520892</v>
       </c>
       <c r="B44" t="n">
         <v>90562</v>
@@ -5364,10 +5354,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>586294</v>
+        <v>586144</v>
       </c>
       <c r="R44" t="n">
-        <v>6617710</v>
+        <v>6617819</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5435,7 +5425,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119520893</v>
+        <v>119520900</v>
       </c>
       <c r="B45" t="n">
         <v>90562</v>
@@ -5475,10 +5465,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>586119</v>
+        <v>586320</v>
       </c>
       <c r="R45" t="n">
-        <v>6617842</v>
+        <v>6617975</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5546,7 +5536,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119520891</v>
+        <v>119520908</v>
       </c>
       <c r="B46" t="n">
         <v>90562</v>
@@ -5586,10 +5576,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>586172</v>
+        <v>586108</v>
       </c>
       <c r="R46" t="n">
-        <v>6617792</v>
+        <v>6617800</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5657,10 +5647,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119520897</v>
+        <v>119520914</v>
       </c>
       <c r="B47" t="n">
-        <v>90562</v>
+        <v>94414</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5669,25 +5659,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>2668</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5697,10 +5687,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586273</v>
+        <v>586225</v>
       </c>
       <c r="R47" t="n">
-        <v>6617904</v>
+        <v>6617957</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5746,7 +5736,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>sten</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5768,10 +5758,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119520886</v>
+        <v>119520947</v>
       </c>
       <c r="B48" t="n">
-        <v>90562</v>
+        <v>84434</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5784,21 +5774,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>241</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5808,10 +5798,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586344</v>
+        <v>586205</v>
       </c>
       <c r="R48" t="n">
-        <v>6617753</v>
+        <v>6618085</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5879,10 +5869,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119520958</v>
+        <v>119520909</v>
       </c>
       <c r="B49" t="n">
-        <v>100171</v>
+        <v>90562</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5891,25 +5881,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5919,10 +5909,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>586121</v>
+        <v>586104</v>
       </c>
       <c r="R49" t="n">
-        <v>6617737</v>
+        <v>6617783</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5965,6 +5955,11 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5985,10 +5980,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119520948</v>
+        <v>119520895</v>
       </c>
       <c r="B50" t="n">
-        <v>105009</v>
+        <v>90562</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5997,25 +5992,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6025,10 +6020,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>586283</v>
+        <v>586158</v>
       </c>
       <c r="R50" t="n">
-        <v>6617615</v>
+        <v>6617877</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6071,6 +6066,11 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -1249,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119520924</v>
+        <v>119520941</v>
       </c>
       <c r="B7" t="n">
-        <v>90846</v>
+        <v>90954</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,34 +1265,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hemfallet ost, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586172</v>
+        <v>586301</v>
       </c>
       <c r="R7" t="n">
-        <v>6617796</v>
+        <v>6617822</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,6 +1331,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1360,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119520941</v>
+        <v>119520924</v>
       </c>
       <c r="B8" t="n">
-        <v>90954</v>
+        <v>90846</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,32 +1375,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6040186</v>
+        <v>658</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hemfallet ost, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586301</v>
+        <v>586172</v>
       </c>
       <c r="R8" t="n">
-        <v>6617822</v>
+        <v>6617796</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1443,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119520949</v>
+        <v>119520937</v>
       </c>
       <c r="B12" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586210</v>
+        <v>586316</v>
       </c>
       <c r="R12" t="n">
-        <v>6617608</v>
+        <v>6617624</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,6 +1883,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1903,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119520937</v>
+        <v>119520949</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,25 +1920,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586316</v>
+        <v>586210</v>
       </c>
       <c r="R13" t="n">
-        <v>6617624</v>
+        <v>6617608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,11 +1994,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -5647,10 +5647,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119520914</v>
+        <v>119520947</v>
       </c>
       <c r="B47" t="n">
-        <v>94414</v>
+        <v>84434</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5659,25 +5659,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2668</v>
+        <v>241</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>586225</v>
+        <v>586205</v>
       </c>
       <c r="R47" t="n">
-        <v>6617957</v>
+        <v>6618085</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>sten</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5758,10 +5758,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119520947</v>
+        <v>119520914</v>
       </c>
       <c r="B48" t="n">
-        <v>84434</v>
+        <v>94414</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5770,25 +5770,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>241</v>
+        <v>2668</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>586205</v>
+        <v>586225</v>
       </c>
       <c r="R48" t="n">
-        <v>6618085</v>
+        <v>6617957</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>sten</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -6094,7 +6094,7 @@
         <v>121201473</v>
       </c>
       <c r="B51" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -6094,7 +6094,7 @@
         <v>121201473</v>
       </c>
       <c r="B51" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -6094,7 +6094,7 @@
         <v>121201473</v>
       </c>
       <c r="B51" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -6094,7 +6094,7 @@
         <v>121201473</v>
       </c>
       <c r="B51" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -6094,7 +6094,7 @@
         <v>121201473</v>
       </c>
       <c r="B51" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -6094,7 +6094,7 @@
         <v>121201473</v>
       </c>
       <c r="B51" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6218,6 +6218,121 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>123276731</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lycksta, Vstm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>586319</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6617786</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Karin Andersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -6223,7 +6223,7 @@
         <v>123276731</v>
       </c>
       <c r="B52" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -6223,7 +6223,7 @@
         <v>123276731</v>
       </c>
       <c r="B52" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -6223,7 +6223,7 @@
         <v>123276731</v>
       </c>
       <c r="B52" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -6223,7 +6223,7 @@
         <v>123276731</v>
       </c>
       <c r="B52" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -6223,7 +6223,7 @@
         <v>123276731</v>
       </c>
       <c r="B52" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -6223,7 +6223,7 @@
         <v>123276731</v>
       </c>
       <c r="B52" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 62438-2019 artfynd.xlsx
+++ b/artfynd/A 62438-2019 artfynd.xlsx
@@ -6223,7 +6223,7 @@
         <v>123276731</v>
       </c>
       <c r="B52" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
